--- a/data/trans_camb/IQ2608_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>19,68</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,3</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-6,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 14,09</t>
+          <t>3,32; 32,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 31,65</t>
+          <t>25,41; 48,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 19,5</t>
+          <t>-31,18; 14,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 32,06</t>
+          <t>-14,28; 14,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,32; 47,57</t>
+          <t>7,58; 32,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 15,21</t>
+          <t>-27,12; 17,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 19,17</t>
+          <t>-1,73; 18,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,39; 36,61</t>
+          <t>19,71; 36,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 11,75</t>
+          <t>-22,79; 8,91</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-15,06%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-1,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>28,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,16%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,8%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,74%</t>
+          <t>-3,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,71%</t>
+          <t>-10,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 23,18</t>
+          <t>4,82; 65,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 53,8</t>
+          <t>36,95; 98,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 31,25</t>
+          <t>-47,96; 26,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 63,23</t>
+          <t>-19,23; 23,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,71; 94,65</t>
+          <t>10,29; 56,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 29,51</t>
+          <t>-38,62; 28,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 33,79</t>
+          <t>-2,39; 32,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,21; 64,43</t>
+          <t>28,21; 64,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 19,74</t>
+          <t>-34,42; 15,71</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>23,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>33,84</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,08</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,15</t>
+          <t>-15,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>-9,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 33,24</t>
+          <t>2,62; 24,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,26; 43,8</t>
+          <t>17,43; 36,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 18,61</t>
+          <t>-24,61; 18,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 23,83</t>
+          <t>12,24; 33,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,35; 35,39</t>
+          <t>23,03; 43,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 20,53</t>
+          <t>-33,89; 3,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 26,34</t>
+          <t>10,71; 25,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,33; 36,92</t>
+          <t>23,74; 37,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 11,08</t>
+          <t>-22,92; 6,83</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-9,13%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>42,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>61,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,39%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,31%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,24%</t>
+          <t>-29,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,88%</t>
+          <t>-16,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 69,49</t>
+          <t>4,23; 47,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,18; 92,24</t>
+          <t>28,09; 72,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 36,8</t>
+          <t>-41,22; 35,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 46,34</t>
+          <t>20,3; 70,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 69,05</t>
+          <t>36,93; 88,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 37,48</t>
+          <t>-59,27; 7,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 51,42</t>
+          <t>18,31; 50,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,71; 72,21</t>
+          <t>39,25; 73,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 19,65</t>
+          <t>-40,85; 12,29</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>48,33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>47,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>28,55</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27,43</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48,33</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,69</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,22</t>
+          <t>27,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27,47</t>
+          <t>26,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,42; 58,38</t>
+          <t>37,43; 57,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 42,2</t>
+          <t>25,31; 48,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 45,86</t>
+          <t>4,05; 43,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 59,4</t>
+          <t>34,74; 58,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,35; 48,88</t>
+          <t>14,27; 41,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 46,53</t>
+          <t>7,84; 45,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,82; 54,83</t>
+          <t>40,29; 55,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,73; 42,46</t>
+          <t>23,94; 42,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,04; 40,36</t>
+          <t>13,45; 39,67</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>113,7%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>105,61%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>63,65%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113,7%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,23; 161,91</t>
+          <t>72,38; 167,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,8; 113,94</t>
+          <t>50,89; 135,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,2; 125,82</t>
+          <t>11,17; 121,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73,4; 174,09</t>
+          <t>64,54; 165,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,14; 142,1</t>
+          <t>26,82; 112,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 126,55</t>
+          <t>16,9; 121,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,93; 144,96</t>
+          <t>81,81; 149,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,48; 113,03</t>
+          <t>48,96; 112,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,35; 103,15</t>
+          <t>29,09; 100,31</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>25,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>31,33</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32,44</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,42</t>
+          <t>-5,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>11,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 38,52</t>
+          <t>8,9; 32,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,51; 43,29</t>
+          <t>20,86; 42,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 20,12</t>
+          <t>15,53; 50,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 33,89</t>
+          <t>12,2; 37,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,36; 42,37</t>
+          <t>18,39; 43,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 48,1</t>
+          <t>-28,56; 22,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 31,5</t>
+          <t>13,67; 32,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,64; 40,26</t>
+          <t>23,07; 40,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 29,11</t>
+          <t>-11,64; 28,18</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57,83%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>66,79%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>50,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>62,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-13,06%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>37,73%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>57,83%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>-11,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,86; 90,2</t>
+          <t>13,53; 67,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,42; 103,73</t>
+          <t>33,32; 89,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 42,1</t>
+          <t>28,95; 108,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,37; 69,14</t>
+          <t>21,4; 88,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,67; 87,44</t>
+          <t>34,11; 103,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,06; 98,69</t>
+          <t>-57,0; 47,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,7; 66,77</t>
+          <t>22,93; 67,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,18; 86,5</t>
+          <t>39,6; 85,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 56,81</t>
+          <t>-19,2; 57,01</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15,74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29,3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>35,98</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>18,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>28,17</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9,91</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,74</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>29,3</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,98</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,17</t>
+          <t>23,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 34,01</t>
+          <t>0,23; 31,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,15; 41,51</t>
+          <t>16,51; 43,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 30,18</t>
+          <t>24,94; 47,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 31,28</t>
+          <t>0,08; 33,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,75; 42,77</t>
+          <t>13,45; 41,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,08; 47,48</t>
+          <t>-15,19; 30,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,27; 28,48</t>
+          <t>7,12; 28,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,46; 37,98</t>
+          <t>20,38; 38,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,36; 35,24</t>
+          <t>9,94; 36,05</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>24,59%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>56,19%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>28,32%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>43,64%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,03; 63,5</t>
+          <t>0,32; 59,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20,83; 78,62</t>
+          <t>21,77; 83,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 53,91</t>
+          <t>33,22; 90,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,26; 57,42</t>
+          <t>0,13; 62,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,65; 82,55</t>
+          <t>17,43; 77,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,72; 90,39</t>
+          <t>-20,99; 53,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,45; 50,91</t>
+          <t>10,08; 50,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,38; 67,78</t>
+          <t>28,4; 68,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,09; 60,23</t>
+          <t>14,73; 62,82</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>24,95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6,27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>42,96</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>22,42</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13,34</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>24,95</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,27</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>12,98</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>7,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>31,67; 54,04</t>
+          <t>13,42; 35,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,72; 36,74</t>
+          <t>-8,21; 19,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 37,77</t>
+          <t>-22,2; 20,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13,89; 36,98</t>
+          <t>30,46; 53,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 20,4</t>
+          <t>7,09; 36,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 22,36</t>
+          <t>-16,22; 36,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,67; 42,04</t>
+          <t>25,0; 42,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,43; 24,1</t>
+          <t>3,62; 24,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 24,68</t>
+          <t>-9,84; 23,09</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>84,77%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>44,24%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>53,32; 133,52</t>
+          <t>18,46; 62,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13,28; 90,02</t>
+          <t>-11,29; 32,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 85,23</t>
+          <t>-30,93; 33,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,3; 63,32</t>
+          <t>50,67; 133,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 33,03</t>
+          <t>11,77; 87,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 36,19</t>
+          <t>-30,19; 80,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,03; 81,73</t>
+          <t>38,11; 82,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,17; 45,64</t>
+          <t>6,04; 45,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 43,33</t>
+          <t>-15,1; 41,55</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>25,45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10,6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12,27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>30,01</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>15,53</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>21,27</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>25,45</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,6</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>18,05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,69</t>
+          <t>15,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>20,72; 39,5</t>
+          <t>16,34; 33,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,65; 25,57</t>
+          <t>1,14; 19,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,54; 36,26</t>
+          <t>-2,55; 25,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16,06; 33,22</t>
+          <t>21,0; 38,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,54; 19,2</t>
+          <t>6,63; 25,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 27,53</t>
+          <t>0,77; 32,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,51; 33,81</t>
+          <t>22,16; 34,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,26</t>
+          <t>6,71; 19,85</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,01; 26,96</t>
+          <t>2,67; 24,96</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>56,34%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>39,93%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>34,5; 84,73</t>
+          <t>24,85; 61,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9,52; 54,68</t>
+          <t>1,68; 35,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,14; 72,62</t>
+          <t>-3,25; 45,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,28; 60,59</t>
+          <t>35,63; 85,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,88; 35,03</t>
+          <t>11,32; 53,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 48,69</t>
+          <t>1,12; 66,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,77; 63,64</t>
+          <t>36,17; 65,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,42; 35,89</t>
+          <t>10,99; 37,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,39; 49,64</t>
+          <t>5,17; 46,41</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-14,95</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-3,7</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-8,73</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,5</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-13,85</t>
+          <t>-6,59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-11,8</t>
+          <t>-11,61</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 3,64</t>
+          <t>-6,98; 6,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 8,79</t>
+          <t>-1,97; 10,47</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 3,83</t>
+          <t>-31,19; -0,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 6,41</t>
+          <t>-10,37; 3,65</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 10,58</t>
+          <t>-4,9; 8,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -0,5</t>
+          <t>-22,67; 5,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,15</t>
+          <t>-6,36; 2,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,97</t>
+          <t>-1,17; 8,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-22,88; -2,06</t>
+          <t>-23,79; -1,63</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-0,64%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-18,12%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-4,5%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-0,64%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-16,79%</t>
+          <t>-8,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-14,34%</t>
+          <t>-14,11%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 4,38</t>
+          <t>-8,22; 8,32</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 11,16</t>
+          <t>-2,26; 13,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 4,75</t>
+          <t>-37,16; -1,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 8,18</t>
+          <t>-12,41; 4,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 13,51</t>
+          <t>-5,68; 11,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,95; -0,7</t>
+          <t>-26,94; 6,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 3,76</t>
+          <t>-7,62; 3,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 9,99</t>
+          <t>-1,42; 10,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -2,66</t>
+          <t>-28,4; -2,06</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>18,28</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>19,69</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>20,28</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>19,93</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,97</t>
+          <t>14,55; 22,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,11</t>
+          <t>15,67; 23,39</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 11,7</t>
+          <t>-2,29; 11,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,03</t>
+          <t>16,15; 23,57</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,27</t>
+          <t>15,95; 23,38</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 12,23</t>
+          <t>-3,81; 10,27</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,67; 22,41</t>
+          <t>16,68; 21,92</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,72</t>
+          <t>17,17; 22,36</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,35</t>
+          <t>-1,22; 9,35</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>33,48%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>25,38; 41,84</t>
+          <t>22,02; 36,57</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>25,82; 41,67</t>
+          <t>23,93; 38,39</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 19,49</t>
+          <t>-3,5; 18,89</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22,16; 36,21</t>
+          <t>25,8; 40,24</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>23,99; 37,97</t>
+          <t>25,25; 40,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 19,44</t>
+          <t>-6,19; 17,34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,15; 37,19</t>
+          <t>26,2; 36,13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>27,21; 37,53</t>
+          <t>26,9; 37,06</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,72; 16,86</t>
+          <t>-1,93; 15,51</t>
         </is>
       </c>
     </row>
